--- a/Récapitulatif_Courses.xlsx
+++ b/Récapitulatif_Courses.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="8" customWidth="1" min="5" max="6"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="8"/>
-    <col width="59" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
@@ -588,6 +588,63 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>pq5ltg0jafgm01jnpklc3gqb74</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>DUPONT</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>12 rue de Paris</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>12 rue de Paris</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Asnières Aller</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>1.0 €</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Chauffeur 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
